--- a/results/job_matches_2026-04-13.xlsx
+++ b/results/job_matches_2026-04-13.xlsx
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Contract Hire (Remote, US Only)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ChowaCo</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, GCP, BigQuery, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080c153a60c2db6d</t>
+          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-13.xlsx
+++ b/results/job_matches_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,33 +503,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Austin, TX, US USA</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>11.8</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c08fc820fe10f7ed</t>
         </is>

--- a/results/job_matches_2026-04-13.xlsx
+++ b/results/job_matches_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>SwapsTech</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,75 +496,145 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
+          <t>https://www.indeed.com/viewjob?jk=4012ccd366ad2714</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Austin, TX, US USA</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D6" t="n">
         <v>11.8</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c08fc820fe10f7ed</t>
         </is>

--- a/results/job_matches_2026-04-13.xlsx
+++ b/results/job_matches_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,105 +538,245 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Sr. Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, EMR, Kinesis, Redshift, S3, Hadoop, Hive, MapReduce, HBase, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
+          <t>https://www.indeed.com/viewjob?jk=454945ebbe7d1ebf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Sr. Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Mirion</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+          <t>https://www.indeed.com/viewjob?jk=56369bdeadc2da7f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Sr. Engineer, Machine Learning</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Poshmark</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Austin, TX, US USA</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D9" t="n">
         <v>11.8</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c08fc820fe10f7ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer, (Production Excellence)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Poshmark</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-13.xlsx
+++ b/results/job_matches_2026-04-13.xlsx
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, EMR, Kinesis, Redshift, S3, Hadoop, Hive, MapReduce, HBase, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
+          <t>https://www.indeed.com/viewjob?jk=454945ebbe7d1ebf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Engineering</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, S3, Hadoop, Hive, MapReduce, HBase, Spark</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454945ebbe7d1ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Platform</t>
+          <t>Sr. Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mirion</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56369bdeadc2da7f</t>
+          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>Sr. Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Mirion</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
+          <t>https://www.indeed.com/viewjob?jk=56369bdeadc2da7f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-13.xlsx
+++ b/results/job_matches_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SwapsTech</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Oracle, MySQL</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4012ccd366ad2714</t>
+          <t>https://www.indeed.com/viewjob?jk=5cdea475a3468daf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Engineering</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>SwapsTech</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, S3, Hadoop, Hive, MapReduce, HBase, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454945ebbe7d1ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=4012ccd366ad2714</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, EMR, Kinesis, Redshift, S3, Hadoop, Hive, MapReduce, HBase, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
+          <t>https://www.indeed.com/viewjob?jk=454945ebbe7d1ebf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,180 +601,320 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
+          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Platform</t>
+          <t>Cloud/Drupal Subject Matter Specialist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mirion</t>
+          <t>BFG Enterprise Services</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Suitland, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56369bdeadc2da7f</t>
+          <t>https://www.indeed.com/viewjob?jk=890c6ef795b6dd39</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Sr. Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
+          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Sr. Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Mirion</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+          <t>https://www.indeed.com/viewjob?jk=56369bdeadc2da7f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Data Architect - C2H</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08fc820fe10f7ed</t>
+          <t>https://www.indeed.com/viewjob?jk=392f54d3fade0b87</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c08fc820fe10f7ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Senior Site Reliability Engineer, (Production Excellence)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Poshmark</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Redwood City, CA, US USA</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D14" t="n">
         <v>10.4</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
         </is>

--- a/results/job_matches_2026-04-13.xlsx
+++ b/results/job_matches_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>SwapsTech</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cdea475a3468daf</t>
+          <t>https://www.indeed.com/viewjob?jk=4012ccd366ad2714</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SwapsTech</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Oracle, MySQL</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4012ccd366ad2714</t>
+          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
         </is>
       </c>
     </row>
@@ -573,95 +573,95 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Mirion</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
+          <t>https://www.indeed.com/viewjob?jk=56369bdeadc2da7f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud/Drupal Subject Matter Specialist</t>
+          <t>Sr. Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BFG Enterprise Services</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Suitland, MD, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=890c6ef795b6dd39</t>
+          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,89 +671,89 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
+          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Platform</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mirion</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56369bdeadc2da7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect - C2H</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=392f54d3fade0b87</t>
+          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,145 +776,75 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
+          <t>https://www.indeed.com/viewjob?jk=c08fc820fe10f7ed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Senior Site Reliability Engineer, (Production Excellence)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c08fc820fe10f7ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Precisely</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer, (Production Excellence)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Poshmark</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Redwood City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
         </is>

--- a/results/job_matches_2026-04-13.xlsx
+++ b/results/job_matches_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Engineer, Software</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Verint Systems Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
+          <t>https://www.indeed.com/viewjob?jk=0c774765a5f06879</t>
         </is>
       </c>
     </row>
@@ -573,52 +573,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Platform</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mirion</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56369bdeadc2da7f</t>
+          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
+          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Sr. Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,137 +671,137 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
+          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Sr. Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Mirion</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
+          <t>https://www.indeed.com/viewjob?jk=56369bdeadc2da7f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>POOLCORP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Covington, LA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+          <t>https://www.indeed.com/viewjob?jk=bdef7c235b1898fd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>William Blair &amp; Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08fc820fe10f7ed</t>
+          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,40 +811,250 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c08fc820fe10f7ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IT Data Developer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tempur + Sealy</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Trinity, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Engineering &amp; Operations Specialist</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Shelter Insurance</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Columbia, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Senior Site Reliability Engineer, (Production Excellence)</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Poshmark</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Redwood City, CA, US USA</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D18" t="n">
         <v>10.4</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
         </is>

--- a/results/job_matches_2026-04-13.xlsx
+++ b/results/job_matches_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior AWS Cloud Engineer - (US - Remote)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SwapsTech</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Oracle, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4012ccd366ad2714</t>
+          <t>https://www.indeed.com/viewjob?jk=03406469e62daa61</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engineer, Software</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Verint Systems Inc.</t>
+          <t>SwapsTech</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c774765a5f06879</t>
+          <t>https://www.indeed.com/viewjob?jk=4012ccd366ad2714</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Engineering</t>
+          <t>Engineer, Software</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Verint Systems Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, S3, Hadoop, Hive, MapReduce, HBase, Spark</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454945ebbe7d1ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=0c774765a5f06879</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
+          <t>https://www.indeed.com/viewjob?jk=83db8f50bcabcd87</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
+          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>Sr. Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
+          <t>AWS, EMR, Kinesis, Redshift, S3, Hadoop, Hive, MapReduce, HBase, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
+          <t>https://www.indeed.com/viewjob?jk=454945ebbe7d1ebf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mirion</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,112 +696,112 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56369bdeadc2da7f</t>
+          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>POOLCORP</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Covington, LA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdef7c235b1898fd</t>
+          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>Mirion</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=56369bdeadc2da7f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Sr. Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,49 +811,49 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
+          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>William Blair &amp; Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
+          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,29 +871,29 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,102 +916,102 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08fc820fe10f7ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT Data Developer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tempur + Sealy</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Trinity, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>IT Data Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Tempur + Sealy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Trinity, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,40 +1021,215 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Sr. Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Purpose Financial</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Greenville, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Purpose Financial</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Greenville, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>California State Personnel Board</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MySQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90079673f1f3efb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Engineering &amp; Operations Specialist</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Shelter Insurance</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Columbia, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Senior Site Reliability Engineer, (Production Excellence)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Poshmark</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Redwood City, CA, US USA</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D23" t="n">
         <v>10.4</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
         </is>

--- a/results/job_matches_2026-04-13.xlsx
+++ b/results/job_matches_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SwapsTech</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4012ccd366ad2714</t>
+          <t>https://www.indeed.com/viewjob?jk=8855ef540e8dc9e8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer, Software</t>
+          <t>Senior Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Verint Systems Inc.</t>
+          <t>Parker Management</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c774765a5f06879</t>
+          <t>https://www.indeed.com/viewjob?jk=43381ea07fee685f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>SwapsTech</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83db8f50bcabcd87</t>
+          <t>https://www.indeed.com/viewjob?jk=4012ccd366ad2714</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Engineer, Software</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Verint Systems Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
+          <t>https://www.indeed.com/viewjob?jk=0c774765a5f06879</t>
         </is>
       </c>
     </row>
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,94 +706,94 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
+          <t>https://www.indeed.com/viewjob?jk=83db8f50bcabcd87</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
+          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Platform</t>
+          <t>Senior Full Stack Engineer - AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mirion</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56369bdeadc2da7f</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
+          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,242 +881,242 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
+          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
+          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IT Data Developer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tempur + Sealy</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Trinity, NC, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Enterprise Architect, Azure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
+          <t>https://www.indeed.com/viewjob?jk=890935458d36553e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
+          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>William Blair &amp; Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90079673f1f3efb8</t>
+          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,77 +1161,392 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
+          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Purpose Financial</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Greenville, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>IT Data Developer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tempur + Sealy</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Trinity, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Purpose Financial</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Greenville, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Purpose Financial</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Greenville, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>California State Personnel Board</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MySQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90079673f1f3efb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Engineering &amp; Operations Specialist</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Shelter Insurance</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Columbia, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Senior Site Reliability Engineer, (Production Excellence)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Poshmark</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Redwood City, CA, US USA</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D31" t="n">
         <v>10.4</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ingeniero de Datos en Azure Cloud</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>EX Squared</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b351fe2c5b197c2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-13.xlsx
+++ b/results/job_matches_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8855ef540e8dc9e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d78327146c19a784</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Integration Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Parker Management</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43381ea07fee685f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4341508fe1c04f1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SwapsTech</t>
+          <t>Parker Management</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4012ccd366ad2714</t>
+          <t>https://www.indeed.com/viewjob?jk=43381ea07fee685f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer, Software</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Verint Systems Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c774765a5f06879</t>
+          <t>https://www.indeed.com/viewjob?jk=8855ef540e8dc9e8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Engineering</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>SwapsTech</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, S3, Hadoop, Hive, MapReduce, HBase, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454945ebbe7d1ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=4012ccd366ad2714</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, IAM, Azure, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83db8f50bcabcd87</t>
+          <t>https://www.indeed.com/viewjob?jk=a52f9c227e61963c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Engineer, Software</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Verint Systems Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
+          <t>https://www.indeed.com/viewjob?jk=0c774765a5f06879</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AI</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=83db8f50bcabcd87</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
+          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, EMR, Kinesis, Redshift, S3, Hadoop, Hive, MapReduce, HBase, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
+          <t>https://www.indeed.com/viewjob?jk=454945ebbe7d1ebf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Engineer - AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cc2730bd14a3e8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
+          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
+          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
+          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Kafka</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=890935458d36553e</t>
+          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
+          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Sr. Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,137 +1161,137 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
+          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AWS Data Architect (Hybrid)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, SQS, SNS, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0e64cf5300616c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Enterprise Architect, Azure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+          <t>https://www.indeed.com/viewjob?jk=890935458d36553e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
+          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IT Data Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tempur + Sealy</t>
+          <t>William Blair &amp; Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Trinity, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,137 +1301,137 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
+          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
+          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Data Engineer/Sr Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90079673f1f3efb8</t>
+          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
+          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, (Production Excellence)</t>
+          <t>IT Data Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Tempur + Sealy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Trinity, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,40 +1511,600 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Sr. Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Purpose Financial</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Greenville, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>O'Fallon, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Purpose Financial</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Greenville, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Platform Architect</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac2463a9d29a6913</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Hifi</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>California State Personnel Board</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MySQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90079673f1f3efb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Data Engineering &amp; Operations Specialist</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Shelter Insurance</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Columbia, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer, (Production Excellence)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Poshmark</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Entry-level Moment Google Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Entry-level Moment Google Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d2f2b3088f910b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Entry-level Moment Google Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f64d013bcc57d616</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Entry-level Moment Google Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6ebc35e151ef300</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Entry-level Moment Google Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f75b248f5282055</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AIA Contract Documents</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1af4727827ae8d39</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Ingeniero de Datos en Azure Cloud</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>EX Squared</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D48" t="n">
         <v>10.4</v>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Azure, Databricks, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2b351fe2c5b197c2</t>
         </is>

--- a/results/job_matches_2026-04-13.xlsx
+++ b/results/job_matches_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Parker Management</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43381ea07fee685f</t>
+          <t>https://www.indeed.com/viewjob?jk=8855ef540e8dc9e8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Parker's Kitchen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8855ef540e8dc9e8</t>
+          <t>https://www.indeed.com/viewjob?jk=403fe46aec3ac312</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SwapsTech</t>
+          <t>Parker Management</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4012ccd366ad2714</t>
+          <t>https://www.indeed.com/viewjob?jk=43381ea07fee685f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SwapsTech</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, IAM, Azure, GCP, Hadoop, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52f9c227e61963c</t>
+          <t>https://www.indeed.com/viewjob?jk=4012ccd366ad2714</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, Kinesis, Redshift, S3, Hadoop, Hive, MapReduce, HBase, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83db8f50bcabcd87</t>
+          <t>https://www.indeed.com/viewjob?jk=454945ebbe7d1ebf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
+          <t>https://www.indeed.com/viewjob?jk=83db8f50bcabcd87</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Engineering</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, S3, Hadoop, Hive, MapReduce, HBase, Spark</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454945ebbe7d1ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=9f47248faf88df34</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
+          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cba17f74f3a8a87</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc5289c2eff0fe3</t>
+          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db447e4c4e1f04b</t>
+          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55ea3b297953077</t>
+          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d857667edacbcc1e</t>
+          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
+          <t>https://www.indeed.com/viewjob?jk=6121915b4e45790d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EMR, Redshift, S3, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529728374eb4213</t>
+          <t>https://www.indeed.com/viewjob?jk=25e97510ea5ed940</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Data Architect (Hybrid)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>William Blair &amp; Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, SQS, SNS, API Gateway, IAM, RDS</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0e64cf5300616c</t>
+          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Azure</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=890935458d36553e</t>
+          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,49 +1266,49 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
+          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,104 +1326,104 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer/Sr Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
+          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr Data Engineer</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
+          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>IT Data Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Tempur + Sealy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Trinity, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IT Data Developer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tempur + Sealy</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Trinity, NC, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1532,38 +1532,38 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr Web Software Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Mouser Electronics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Mansfield, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
+          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Hifi</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
+          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2463a9d29a6913</t>
+          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hifi</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90079673f1f3efb8</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
+          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, (Production Excellence)</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
+          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Entry-level Moment Google Contact Center Developer</t>
+          <t>Data Engineering &amp; Operations Specialist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Entry-level Moment Google Contact Center Developer</t>
+          <t>Senior Site Reliability Engineer, (Production Excellence)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d2f2b3088f910b3</t>
+          <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Entry-level Moment Google Contact Center Developer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64d013bcc57d616</t>
+          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Entry-level Moment Google Contact Center Developer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ebc35e151ef300</t>
+          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Entry-level Moment Google Contact Center Developer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f75b248f5282055</t>
+          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Entry-level Moment Google Contact Center Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AIA Contract Documents</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
+          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AIA Contract Documents</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af4727827ae8d39</t>
+          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
         </is>
       </c>
     </row>
@@ -2107,6 +2107,41 @@
       <c r="G48" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2b351fe2c5b197c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-13.xlsx
+++ b/results/job_matches_2026-04-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=72b0fdeb9512d34e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b78c747cdda3eb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sys. Integration Sr. Specialist Advisor</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>William Blair &amp; Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,49 +1266,49 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
+          <t>https://www.indeed.com/viewjob?jk=cea3dbea7cb13bbf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5622a97c0cb32459</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Sys. Integration Sr. Specialist Advisor</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,139 +1326,139 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
+          <t>https://www.indeed.com/viewjob?jk=1aca172869e592e8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
+          <t>https://www.indeed.com/viewjob?jk=c2444333527505cd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
+          <t>https://www.indeed.com/viewjob?jk=ee60578e0abfdb96</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, Glue, Lambda, Redshift, IAM, RDS, Spark, PySpark, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
+          <t>https://www.indeed.com/viewjob?jk=8b32f7b404908120</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IT Data Developer</t>
+          <t>Data Engineer/Sr Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tempur + Sealy</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Trinity, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,49 +1476,49 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f129032e6f84d172</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ed57d3552234a972</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1532,46 +1532,46 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
+          <t>https://www.indeed.com/viewjob?jk=f675cb5511b3a92e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Web Software Developer</t>
+          <t>IT Data Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mouser Electronics</t>
+          <t>Tempur + Sealy</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mansfield, TX, US USA</t>
+          <t>Trinity, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Spark, PySpark, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d7106826dcc9d2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hifi</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
+          <t>https://www.indeed.com/viewjob?jk=10b40f262a4271a7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e4bcd62747c894</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>JobSPOT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
+          <t>https://www.indeed.com/viewjob?jk=d30905e392635ceb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Sr Web Software Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Mouser Electronics</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Mansfield, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=336c0c1bf86693ef</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Hifi</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
+          <t>https://www.indeed.com/viewjob?jk=7522730840daa67d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
+          <t>https://www.indeed.com/viewjob?jk=27d727c9d934f72b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Path Robotics, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0c06f03d80ad17</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3e97aaf28d0108</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, (Production Excellence)</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
+          <t>https://www.indeed.com/viewjob?jk=410def4f54721f1a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c2e004e287ec36</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b55d3d996d9d61dc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=faf1e7e97badd9a1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Entry-level Moment Google Contact Center Developer</t>
+          <t>Data Engineering &amp; Operations Specialist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0786555ef46de3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer, (Production Excellence)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AIA Contract Documents</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
+          <t>https://www.indeed.com/viewjob?jk=f706322313ef04c9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ingeniero de Datos en Azure Cloud</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EX Squared</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b351fe2c5b197c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f21cb7010e5a8a63</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,15 +2131,190 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a6d4850de30c8ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc22d977c810f0a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Entry-level Moment Google Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26650088972ec91e</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>AIA Contract Documents</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27b382a0dd9b7c72</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Ingeniero de Datos en Azure Cloud</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>EX Squared</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b351fe2c5b197c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Solution Engineer - Data Engineering Specialist - Bilingual (Spanish)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=92a26823ec6dae45</t>
         </is>
